--- a/Hyundai_SND96_CityColor_Quotation.xlsx
+++ b/Hyundai_SND96_CityColor_Quotation.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Quotation" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Quotation!$A$1:$F$70</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Quotation!$A$1:$F$68</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="76">
   <si>
     <t xml:space="preserve">QUOTATION</t>
   </si>
@@ -148,7 +148,7 @@
     <t xml:space="preserve">Nos</t>
   </si>
   <si>
-    <t xml:space="preserve">Rental for 15 days @ SAR 125 per unit per day</t>
+    <t xml:space="preserve">Rental for 15 days @ SAR 160 per unit per day</t>
   </si>
   <si>
     <t xml:space="preserve">Transportation to Site</t>
@@ -220,13 +220,7 @@
     <t xml:space="preserve">Cost per Showroom</t>
   </si>
   <si>
-    <t xml:space="preserve">Subtotal — All 9 Showrooms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saudi National Day 96 Goodwill Discount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NET TOTAL (excl. VAT)</t>
+    <t xml:space="preserve">TOTAL PROJECT VALUE — All 9 Showrooms (excl. VAT)</t>
   </si>
   <si>
     <t xml:space="preserve">VAT (15%)</t>
@@ -244,7 +238,7 @@
     <t xml:space="preserve">5.  IMPORTANT NOTES &amp; TERMS</t>
   </si>
   <si>
-    <t xml:space="preserve">•  The rate of SAR 125 per City-Color per day is all-inclusive, covering rental, transportation, installation, accessories, testing, commissioning, technical support, dismantling and removal.</t>
+    <t xml:space="preserve">•  The rate of SAR 160 per City-Color per day is all-inclusive, covering rental, transportation, installation, accessories, testing, commissioning, technical support, dismantling and removal.</t>
   </si>
   <si>
     <t xml:space="preserve">•  Pricing is based on standard installation conditions. Any special access requirements (crane, boom lift, scaffolding, special permits, major electrical works, etc.) will be quoted separately after site assessment.</t>
@@ -267,15 +261,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="General"/>
     <numFmt numFmtId="167" formatCode="0"/>
-    <numFmt numFmtId="168" formatCode="#,##0;\(#,##0\)"/>
-    <numFmt numFmtId="169" formatCode="#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -415,14 +408,6 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
@@ -453,7 +438,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -490,12 +475,6 @@
         <bgColor rgb="FFF4FAFA"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
-        <bgColor rgb="FFF4FAFA"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
@@ -546,7 +525,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -687,31 +666,27 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -744,7 +719,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF3CD"/>
+      <rgbColor rgb="FFF4FAFA"/>
       <rgbColor rgb="FFE8F2F3"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -759,7 +734,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFF4FAFA"/>
+      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -1009,7 +984,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A2:F70"/>
+  <dimension ref="A2:F68"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1170,11 +1145,11 @@
         <v>15</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F19" s="15" t="n">
         <f aca="false">C19*D19*E19</f>
-        <v>18750</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1191,11 +1166,11 @@
         <v>15</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F20" s="20" t="n">
         <f aca="false">C20*D20*E20</f>
-        <v>18750</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1212,11 +1187,11 @@
         <v>15</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F21" s="15" t="n">
         <f aca="false">C21*D21*E21</f>
-        <v>18750</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1233,11 +1208,11 @@
         <v>15</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F22" s="20" t="n">
         <f aca="false">C22*D22*E22</f>
-        <v>18750</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1254,11 +1229,11 @@
         <v>15</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F23" s="15" t="n">
         <f aca="false">C23*D23*E23</f>
-        <v>18750</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1275,11 +1250,11 @@
         <v>15</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F24" s="20" t="n">
         <f aca="false">C24*D24*E24</f>
-        <v>18750</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1296,11 +1271,11 @@
         <v>15</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F25" s="15" t="n">
         <f aca="false">C25*D25*E25</f>
-        <v>18750</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1317,11 +1292,11 @@
         <v>15</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F26" s="20" t="n">
         <f aca="false">C26*D26*E26</f>
-        <v>18750</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1338,11 +1313,11 @@
         <v>15</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F27" s="15" t="n">
         <f aca="false">C27*D27*E27</f>
-        <v>18750</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1362,7 +1337,7 @@
       </c>
       <c r="F28" s="23" t="n">
         <f aca="false">SUM(F19:F27)</f>
-        <v>168750</v>
+        <v>216000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1678,7 +1653,7 @@
       <c r="D50" s="7"/>
       <c r="E50" s="32" t="n">
         <f aca="false">E19</f>
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F50" s="32"/>
     </row>
@@ -1691,7 +1666,7 @@
       <c r="D51" s="7"/>
       <c r="E51" s="32" t="n">
         <f aca="false">E19*15</f>
-        <v>1875</v>
+        <v>2400</v>
       </c>
       <c r="F51" s="32"/>
     </row>
@@ -1704,7 +1679,7 @@
       <c r="D52" s="7"/>
       <c r="E52" s="32" t="n">
         <f aca="false">F19</f>
-        <v>18750</v>
+        <v>24000</v>
       </c>
       <c r="F52" s="32"/>
     </row>
@@ -1717,7 +1692,7 @@
       <c r="D53" s="33"/>
       <c r="E53" s="34" t="n">
         <f aca="false">F28</f>
-        <v>168750</v>
+        <v>216000</v>
       </c>
       <c r="F53" s="34"/>
     </row>
@@ -1729,122 +1704,107 @@
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
       <c r="E54" s="35" t="n">
-        <v>-750</v>
+        <f aca="false">ROUND(E53*0.15,2)</f>
+        <v>32400</v>
       </c>
       <c r="F54" s="35"/>
     </row>
-    <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="33" t="s">
+    <row r="55" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="B55" s="33"/>
-      <c r="C55" s="33"/>
-      <c r="D55" s="33"/>
-      <c r="E55" s="34" t="n">
-        <f aca="false">F28+E54</f>
-        <v>168000</v>
-      </c>
-      <c r="F55" s="34"/>
-    </row>
-    <row r="56" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7" t="s">
+      <c r="B55" s="36"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="36"/>
+      <c r="E55" s="37" t="n">
+        <f aca="false">E53+E54</f>
+        <v>248400</v>
+      </c>
+      <c r="F55" s="37"/>
+    </row>
+    <row r="57" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="36" t="n">
-        <f aca="false">ROUND(E55*0.15,2)</f>
-        <v>25200</v>
-      </c>
-      <c r="F56" s="36"/>
-    </row>
-    <row r="57" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="37" t="s">
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+    </row>
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="B57" s="37"/>
-      <c r="C57" s="37"/>
-      <c r="D57" s="37"/>
-      <c r="E57" s="38" t="n">
-        <f aca="false">E55+E56</f>
-        <v>193200</v>
-      </c>
-      <c r="F57" s="38"/>
-    </row>
-    <row r="59" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="9" t="s">
+      <c r="B58" s="38"/>
+      <c r="C58" s="38"/>
+      <c r="D58" s="38"/>
+      <c r="E58" s="38"/>
+      <c r="F58" s="38"/>
+    </row>
+    <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-    </row>
-    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="39" t="s">
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+    </row>
+    <row r="61" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="B60" s="39"/>
-      <c r="C60" s="39"/>
-      <c r="D60" s="39"/>
-      <c r="E60" s="39"/>
-      <c r="F60" s="39"/>
-    </row>
-    <row r="62" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="9" t="s">
+      <c r="B61" s="39"/>
+      <c r="C61" s="39"/>
+      <c r="D61" s="39"/>
+      <c r="E61" s="39"/>
+      <c r="F61" s="39"/>
+    </row>
+    <row r="62" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
+      <c r="B62" s="39"/>
+      <c r="C62" s="39"/>
+      <c r="D62" s="39"/>
+      <c r="E62" s="39"/>
+      <c r="F62" s="39"/>
     </row>
     <row r="63" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="40" t="s">
+      <c r="A63" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="B63" s="40"/>
-      <c r="C63" s="40"/>
-      <c r="D63" s="40"/>
-      <c r="E63" s="40"/>
-      <c r="F63" s="40"/>
-    </row>
-    <row r="64" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="40" t="s">
+      <c r="B63" s="39"/>
+      <c r="C63" s="39"/>
+      <c r="D63" s="39"/>
+      <c r="E63" s="39"/>
+      <c r="F63" s="39"/>
+    </row>
+    <row r="64" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="B64" s="40"/>
-      <c r="C64" s="40"/>
-      <c r="D64" s="40"/>
-      <c r="E64" s="40"/>
-      <c r="F64" s="40"/>
-    </row>
-    <row r="65" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="40" t="s">
+      <c r="B64" s="39"/>
+      <c r="C64" s="39"/>
+      <c r="D64" s="39"/>
+      <c r="E64" s="39"/>
+      <c r="F64" s="39"/>
+    </row>
+    <row r="65" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="B65" s="40"/>
-      <c r="C65" s="40"/>
-      <c r="D65" s="40"/>
-      <c r="E65" s="40"/>
-      <c r="F65" s="40"/>
-    </row>
-    <row r="66" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="40" t="s">
+      <c r="B65" s="39"/>
+      <c r="C65" s="39"/>
+      <c r="D65" s="39"/>
+      <c r="E65" s="39"/>
+      <c r="F65" s="39"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="40" t="s">
         <v>75</v>
-      </c>
-      <c r="B66" s="40"/>
-      <c r="C66" s="40"/>
-      <c r="D66" s="40"/>
-      <c r="E66" s="40"/>
-      <c r="F66" s="40"/>
-    </row>
-    <row r="67" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="40" t="s">
-        <v>76</v>
       </c>
       <c r="B67" s="40"/>
       <c r="C67" s="40"/>
@@ -1852,26 +1812,16 @@
       <c r="E67" s="40"/>
       <c r="F67" s="40"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="B69" s="41"/>
-      <c r="C69" s="41"/>
-      <c r="D69" s="41"/>
-      <c r="E69" s="41"/>
-      <c r="F69" s="41"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="41"/>
-      <c r="B70" s="41"/>
-      <c r="C70" s="41"/>
-      <c r="D70" s="41"/>
-      <c r="E70" s="41"/>
-      <c r="F70" s="41"/>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="40"/>
+      <c r="B68" s="40"/>
+      <c r="C68" s="40"/>
+      <c r="D68" s="40"/>
+      <c r="E68" s="40"/>
+      <c r="F68" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="65">
+  <mergeCells count="61">
     <mergeCell ref="D2:F5"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A10:F10"/>
@@ -1924,19 +1874,15 @@
     <mergeCell ref="E54:F54"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E55:F55"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A58:F58"/>
     <mergeCell ref="A60:F60"/>
+    <mergeCell ref="A61:F61"/>
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="A64:F64"/>
     <mergeCell ref="A65:F65"/>
-    <mergeCell ref="A66:F66"/>
-    <mergeCell ref="A67:F67"/>
-    <mergeCell ref="A69:F70"/>
+    <mergeCell ref="A67:F68"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.511811023622047" footer="0.5"/>

--- a/Hyundai_SND96_CityColor_Quotation.xlsx
+++ b/Hyundai_SND96_CityColor_Quotation.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Quotation" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Quotation!$A$1:$F$68</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Quotation!$A$1:$F$77</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="80">
   <si>
     <t xml:space="preserve">QUOTATION</t>
   </si>
@@ -251,6 +251,18 @@
   </si>
   <si>
     <t xml:space="preserve">•  All prices are in Saudi Riyals (SAR) and exclude 15% VAT, shown separately above.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For &amp; on behalf of — MIRADORE EXPERIENCES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIENT ACCEPTANCE — HYUNDAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Authorized Signatory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signature, Company Stamp &amp; Date</t>
   </si>
   <si>
     <t xml:space="preserve">MIRADORE EXPERIENCES — RIYADH, KINGDOM OF SAUDI ARABIA
@@ -476,7 +488,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -499,6 +511,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF5B6B6E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -525,7 +546,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -684,6 +705,14 @@
     </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -790,6 +819,80 @@
         <a:xfrm>
           <a:off x="444600" y="190440"/>
           <a:ext cx="2857320" cy="780840"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>76320</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>171360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2124000</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>56880</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Image 2" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="520920" y="15211440"/>
+          <a:ext cx="2047680" cy="723600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1428840</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>19080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2419200</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>171360</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 3" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1873440" y="15059160"/>
+          <a:ext cx="990360" cy="990360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -984,7 +1087,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A2:F68"/>
+  <dimension ref="A2:F77"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1802,26 +1905,55 @@
       <c r="E65" s="39"/>
       <c r="F65" s="39"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="40" t="s">
         <v>75</v>
       </c>
       <c r="B67" s="40"/>
       <c r="C67" s="40"/>
-      <c r="D67" s="40"/>
+      <c r="D67" s="40" t="s">
+        <v>76</v>
+      </c>
       <c r="E67" s="40"/>
       <c r="F67" s="40"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="40"/>
-      <c r="B68" s="40"/>
-      <c r="C68" s="40"/>
-      <c r="D68" s="40"/>
-      <c r="E68" s="40"/>
-      <c r="F68" s="40"/>
+    <row r="68" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="69" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="70" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="71" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="72" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="73" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="B74" s="41"/>
+      <c r="D74" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E74" s="41"/>
+      <c r="F74" s="41"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="B76" s="42"/>
+      <c r="C76" s="42"/>
+      <c r="D76" s="42"/>
+      <c r="E76" s="42"/>
+      <c r="F76" s="42"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="42"/>
+      <c r="B77" s="42"/>
+      <c r="C77" s="42"/>
+      <c r="D77" s="42"/>
+      <c r="E77" s="42"/>
+      <c r="F77" s="42"/>
     </row>
   </sheetData>
-  <mergeCells count="61">
+  <mergeCells count="65">
     <mergeCell ref="D2:F5"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A10:F10"/>
@@ -1882,7 +2014,11 @@
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="A64:F64"/>
     <mergeCell ref="A65:F65"/>
-    <mergeCell ref="A67:F68"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="A76:F77"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.511811023622047" footer="0.5"/>

--- a/Hyundai_SND96_CityColor_Quotation.xlsx
+++ b/Hyundai_SND96_CityColor_Quotation.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Quotation" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Quotation!$A$1:$F$77</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Quotation!$A$1:$F$78</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="77">
   <si>
     <t xml:space="preserve">QUOTATION</t>
   </si>
@@ -37,37 +37,28 @@
     <t xml:space="preserve">Client:  Hyundai — Showrooms Network, KSA</t>
   </si>
   <si>
-    <t xml:space="preserve">Quotation Ref:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIR-HYN-SND96-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Installation Date:  16 September 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quotation Date:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04 September 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dismantling Date:  30 September 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Currency:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saudi Riyal (SAR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rental Duration:  15 Days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prices:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excluding 15% VAT</t>
+    <t xml:space="preserve">Quotation Ref: MIR-HYN-SND96-001   ·   04 September 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSTALLATION DATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISMANTLING DATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENTAL DURATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 September 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 September 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 Days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Currency: Saudi Riyal (SAR)   ·   Prices exclude 15% VAT, shown separately in the commercial summary</t>
   </si>
   <si>
     <t xml:space="preserve">1.  LOCATION-WISE BOQ</t>
@@ -208,9 +199,6 @@
     <t xml:space="preserve">Rental Duration</t>
   </si>
   <si>
-    <t xml:space="preserve">15 Days</t>
-  </si>
-  <si>
     <t xml:space="preserve">Daily Rate (per City-Color)</t>
   </si>
   <si>
@@ -259,10 +247,13 @@
     <t xml:space="preserve">CLIENT ACCEPTANCE — HYUNDAI</t>
   </si>
   <si>
+    <t xml:space="preserve">Adeel Ahmad — Director</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signature, Company Stamp &amp; Date</t>
+  </si>
+  <si>
     <t xml:space="preserve">Authorized Signatory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signature, Company Stamp &amp; Date</t>
   </si>
   <si>
     <t xml:space="preserve">MIRADORE EXPERIENCES — RIYADH, KINGDOM OF SAUDI ARABIA
@@ -280,7 +271,7 @@
     <numFmt numFmtId="167" formatCode="0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -314,20 +305,160 @@
     <font>
       <b val="true"/>
       <sz val="15"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10.5"/>
       <color rgb="FF1F2A2C"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF1F2A2C"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <color rgb="FF0F6E78"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F2A2C"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="8.5"/>
+      <color rgb="FF5B6B6E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF1F2A2C"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9.5"/>
+      <color rgb="FF1F2A2C"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF5B6B6E"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF5B6B6E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9.5"/>
+      <color rgb="FF0F6E78"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF1F2A2C"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -342,101 +473,8 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="11.5"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9.5"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9.5"/>
-      <color rgb="FF1F2A2C"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9.5"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9.5"/>
-      <color rgb="FF1F2A2C"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10.5"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <sz val="8.5"/>
       <color rgb="FF5B6B6E"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF5B6B6E"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF1F2A2C"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9.5"/>
-      <color rgb="FF0F6E78"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF1F2A2C"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -465,12 +503,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAFA"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF0F6E78"/>
         <bgColor rgb="FF008080"/>
       </patternFill>
@@ -483,12 +515,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAFA"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE8F2F3"/>
         <bgColor rgb="FFF4FAFA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -512,6 +550,32 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFC9DADD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC9DADD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9DADD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFC9DADD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC9DADD"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFC9DADD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top style="thin">
@@ -546,7 +610,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -559,163 +623,179 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -841,7 +921,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>2124000</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>56880</xdr:rowOff>
+      <xdr:rowOff>56520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -854,7 +934,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="520920" y="15211440"/>
+          <a:off x="520920" y="15496920"/>
           <a:ext cx="2047680" cy="723600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -870,15 +950,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1428840</xdr:colOff>
+      <xdr:colOff>1333440</xdr:colOff>
       <xdr:row>67</xdr:row>
       <xdr:rowOff>19080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2419200</xdr:colOff>
+      <xdr:colOff>2599920</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>171360</xdr:rowOff>
+      <xdr:rowOff>161280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -891,8 +971,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1873440" y="15059160"/>
-          <a:ext cx="990360" cy="990360"/>
+          <a:off x="1778040" y="15344640"/>
+          <a:ext cx="1266480" cy="980640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1087,7 +1167,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A2:F77"/>
+  <dimension ref="A2:F78"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1128,7 +1208,7 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>1</v>
       </c>
@@ -1148,774 +1228,768 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B12" s="5"/>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5"/>
+      <c r="D12" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="B13" s="7"/>
+      <c r="C13" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="8" t="s">
+      <c r="D13" s="7"/>
+      <c r="E13" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="7" t="s">
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="6" t="s">
+      <c r="D14" s="8"/>
+      <c r="E14" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2"/>
+      <c r="B17" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="8" t="s">
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="7" t="s">
+      <c r="B18" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
+      <c r="C18" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-    </row>
-    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
+      <c r="D18" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="E18" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="F18" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="10" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="E19" s="15" t="n">
         <v>160</v>
       </c>
-      <c r="F19" s="15" t="n">
+      <c r="F19" s="16" t="n">
         <f aca="false">C19*D19*E19</f>
         <v>24000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="18" t="n">
+      <c r="B20" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="D20" s="18" t="n">
+      <c r="D20" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="E20" s="19" t="n">
+      <c r="E20" s="20" t="n">
         <v>160</v>
       </c>
-      <c r="F20" s="20" t="n">
+      <c r="F20" s="21" t="n">
         <f aca="false">C20*D20*E20</f>
         <v>24000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="13" t="n">
+      <c r="B21" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="E21" s="14" t="n">
+      <c r="E21" s="15" t="n">
         <v>160</v>
       </c>
-      <c r="F21" s="15" t="n">
+      <c r="F21" s="16" t="n">
         <f aca="false">C21*D21*E21</f>
         <v>24000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B22" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="18" t="n">
+      <c r="B22" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="18" t="n">
+      <c r="D22" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="E22" s="19" t="n">
+      <c r="E22" s="20" t="n">
         <v>160</v>
       </c>
-      <c r="F22" s="20" t="n">
+      <c r="F22" s="21" t="n">
         <f aca="false">C22*D22*E22</f>
         <v>24000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B23" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="13" t="n">
+      <c r="B23" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="E23" s="14" t="n">
+      <c r="E23" s="15" t="n">
         <v>160</v>
       </c>
-      <c r="F23" s="15" t="n">
+      <c r="F23" s="16" t="n">
         <f aca="false">C23*D23*E23</f>
         <v>24000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="B24" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="18" t="n">
+      <c r="B24" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D24" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="E24" s="19" t="n">
+      <c r="E24" s="20" t="n">
         <v>160</v>
       </c>
-      <c r="F24" s="20" t="n">
+      <c r="F24" s="21" t="n">
         <f aca="false">C24*D24*E24</f>
         <v>24000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B25" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="13" t="n">
+      <c r="B25" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="E25" s="14" t="n">
+      <c r="E25" s="15" t="n">
         <v>160</v>
       </c>
-      <c r="F25" s="15" t="n">
+      <c r="F25" s="16" t="n">
         <f aca="false">C25*D25*E25</f>
         <v>24000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B26" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="18" t="n">
+      <c r="B26" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="18" t="n">
+      <c r="D26" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="E26" s="19" t="n">
+      <c r="E26" s="20" t="n">
         <v>160</v>
       </c>
-      <c r="F26" s="20" t="n">
+      <c r="F26" s="21" t="n">
         <f aca="false">C26*D26*E26</f>
         <v>24000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B27" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="13" t="n">
+      <c r="B27" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="E27" s="14" t="n">
+      <c r="E27" s="15" t="n">
         <v>160</v>
       </c>
-      <c r="F27" s="15" t="n">
+      <c r="F27" s="16" t="n">
         <f aca="false">C27*D27*E27</f>
         <v>24000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="22" t="n">
+      <c r="A28" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="22"/>
+      <c r="C28" s="23" t="n">
         <f aca="false">SUM(C19:C27)</f>
         <v>90</v>
       </c>
-      <c r="D28" s="22" t="n">
+      <c r="D28" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="E28" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" s="23" t="n">
+      <c r="E28" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" s="24" t="n">
         <f aca="false">SUM(F19:F27)</f>
         <v>216000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="2"/>
+      <c r="B30" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+    </row>
+    <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-    </row>
-    <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B31" s="24" t="s">
+      <c r="E31" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="F31" s="25"/>
+    </row>
+    <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="C32" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E31" s="24" t="s">
+      <c r="E32" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="F31" s="24"/>
-    </row>
-    <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11" t="n">
+      <c r="F32" s="27"/>
+    </row>
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B32" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="11" t="n">
+      <c r="D33" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="29"/>
+    </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="F34" s="30"/>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D35" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="F35" s="29"/>
+    </row>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="F36" s="30"/>
+    </row>
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E32" s="26" t="s">
+      <c r="E37" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="F32" s="26"/>
-    </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B33" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="16" t="n">
+      <c r="F37" s="29"/>
+    </row>
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="E33" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="F33" s="28"/>
-    </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B34" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="11" t="n">
+      <c r="D38" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" s="30"/>
+    </row>
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B39" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E34" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="F34" s="29"/>
-    </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B35" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C35" s="16" t="n">
+      <c r="D39" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="F39" s="29"/>
+    </row>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40" s="30"/>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="D35" s="16" t="s">
+      <c r="B41" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E35" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="F35" s="28"/>
-    </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B36" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="11" t="n">
+      <c r="E41" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="F41" s="29"/>
+    </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="D36" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E36" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="F36" s="29"/>
-    </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="B37" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C37" s="16" t="n">
+      <c r="D42" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E42" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="F42" s="30"/>
+    </row>
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="E37" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="F37" s="28"/>
-    </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="B38" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="C38" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E38" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="F38" s="29"/>
-    </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B39" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="C39" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="E39" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="F39" s="28"/>
-    </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B40" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="C40" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E40" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="F40" s="29"/>
-    </row>
-    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="B41" s="27" t="s">
+      <c r="D43" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E43" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="F43" s="29"/>
+    </row>
+    <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2"/>
+      <c r="B45" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="E41" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="F41" s="28"/>
-    </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="B42" s="25" t="s">
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+    </row>
+    <row r="46" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E42" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="F42" s="29"/>
-    </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="B43" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="C43" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="E43" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="F43" s="28"/>
-    </row>
-    <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-    </row>
-    <row r="46" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="30" t="n">
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="32" t="n">
         <f aca="false">COUNTA(B19:B27)</f>
         <v>9</v>
       </c>
-      <c r="F46" s="30"/>
+      <c r="F46" s="32"/>
     </row>
     <row r="47" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="30" t="n">
+      <c r="A47" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F47" s="30"/>
+      <c r="F47" s="32"/>
     </row>
     <row r="48" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="30" t="n">
+      <c r="A48" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="32" t="n">
         <f aca="false">C28</f>
         <v>90</v>
       </c>
-      <c r="F48" s="30"/>
+      <c r="F48" s="32"/>
     </row>
     <row r="49" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="F49" s="31"/>
+      <c r="A49" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="31"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="33"/>
     </row>
     <row r="50" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="32" t="n">
+      <c r="A50" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="31"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="31"/>
+      <c r="E50" s="34" t="n">
         <f aca="false">E19</f>
         <v>160</v>
       </c>
-      <c r="F50" s="32"/>
+      <c r="F50" s="34"/>
     </row>
     <row r="51" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="32" t="n">
+      <c r="A51" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="31"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="34" t="n">
         <f aca="false">E19*15</f>
         <v>2400</v>
       </c>
-      <c r="F51" s="32"/>
+      <c r="F51" s="34"/>
     </row>
     <row r="52" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="32" t="n">
+      <c r="A52" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="31"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="34" t="n">
         <f aca="false">F19</f>
         <v>24000</v>
       </c>
-      <c r="F52" s="32"/>
-    </row>
-    <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="B53" s="33"/>
-      <c r="C53" s="33"/>
-      <c r="D53" s="33"/>
-      <c r="E53" s="34" t="n">
+      <c r="F52" s="34"/>
+    </row>
+    <row r="53" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="35"/>
+      <c r="C53" s="35"/>
+      <c r="D53" s="35"/>
+      <c r="E53" s="36" t="n">
         <f aca="false">F28</f>
         <v>216000</v>
       </c>
-      <c r="F53" s="34"/>
+      <c r="F53" s="36"/>
     </row>
     <row r="54" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="35" t="n">
+      <c r="A54" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="31"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="31"/>
+      <c r="E54" s="37" t="n">
         <f aca="false">ROUND(E53*0.15,2)</f>
         <v>32400</v>
       </c>
-      <c r="F54" s="35"/>
-    </row>
-    <row r="55" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="B55" s="36"/>
-      <c r="C55" s="36"/>
-      <c r="D55" s="36"/>
-      <c r="E55" s="37" t="n">
+      <c r="F54" s="37"/>
+    </row>
+    <row r="55" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="38"/>
+      <c r="C55" s="38"/>
+      <c r="D55" s="38"/>
+      <c r="E55" s="39" t="n">
         <f aca="false">E53+E54</f>
         <v>248400</v>
       </c>
-      <c r="F55" s="37"/>
+      <c r="F55" s="39"/>
     </row>
     <row r="57" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="9" t="s">
+      <c r="A57" s="2"/>
+      <c r="B57" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+    </row>
+    <row r="58" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="40"/>
+      <c r="C58" s="40"/>
+      <c r="D58" s="40"/>
+      <c r="E58" s="40"/>
+      <c r="F58" s="40"/>
+    </row>
+    <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2"/>
+      <c r="B60" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C60" s="10"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="10"/>
+    </row>
+    <row r="61" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61" s="41"/>
+      <c r="C61" s="41"/>
+      <c r="D61" s="41"/>
+      <c r="E61" s="41"/>
+      <c r="F61" s="41"/>
+    </row>
+    <row r="62" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-    </row>
-    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="38" t="s">
+      <c r="B62" s="41"/>
+      <c r="C62" s="41"/>
+      <c r="D62" s="41"/>
+      <c r="E62" s="41"/>
+      <c r="F62" s="41"/>
+    </row>
+    <row r="63" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="B58" s="38"/>
-      <c r="C58" s="38"/>
-      <c r="D58" s="38"/>
-      <c r="E58" s="38"/>
-      <c r="F58" s="38"/>
-    </row>
-    <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="9" t="s">
+      <c r="B63" s="41"/>
+      <c r="C63" s="41"/>
+      <c r="D63" s="41"/>
+      <c r="E63" s="41"/>
+      <c r="F63" s="41"/>
+    </row>
+    <row r="64" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-    </row>
-    <row r="61" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="39" t="s">
+      <c r="B64" s="41"/>
+      <c r="C64" s="41"/>
+      <c r="D64" s="41"/>
+      <c r="E64" s="41"/>
+      <c r="F64" s="41"/>
+    </row>
+    <row r="65" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="B61" s="39"/>
-      <c r="C61" s="39"/>
-      <c r="D61" s="39"/>
-      <c r="E61" s="39"/>
-      <c r="F61" s="39"/>
-    </row>
-    <row r="62" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="39" t="s">
+      <c r="B65" s="41"/>
+      <c r="C65" s="41"/>
+      <c r="D65" s="41"/>
+      <c r="E65" s="41"/>
+      <c r="F65" s="41"/>
+    </row>
+    <row r="67" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="B62" s="39"/>
-      <c r="C62" s="39"/>
-      <c r="D62" s="39"/>
-      <c r="E62" s="39"/>
-      <c r="F62" s="39"/>
-    </row>
-    <row r="63" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="39" t="s">
+      <c r="B67" s="42"/>
+      <c r="C67" s="42"/>
+      <c r="D67" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="B63" s="39"/>
-      <c r="C63" s="39"/>
-      <c r="D63" s="39"/>
-      <c r="E63" s="39"/>
-      <c r="F63" s="39"/>
-    </row>
-    <row r="64" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="B64" s="39"/>
-      <c r="C64" s="39"/>
-      <c r="D64" s="39"/>
-      <c r="E64" s="39"/>
-      <c r="F64" s="39"/>
-    </row>
-    <row r="65" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="B65" s="39"/>
-      <c r="C65" s="39"/>
-      <c r="D65" s="39"/>
-      <c r="E65" s="39"/>
-      <c r="F65" s="39"/>
-    </row>
-    <row r="67" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="B67" s="40"/>
-      <c r="C67" s="40"/>
-      <c r="D67" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="E67" s="40"/>
-      <c r="F67" s="40"/>
+      <c r="E67" s="42"/>
+      <c r="F67" s="42"/>
     </row>
     <row r="68" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="69" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1924,54 +1998,57 @@
     <row r="72" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="73" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="B74" s="41"/>
-      <c r="D74" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E74" s="41"/>
-      <c r="F74" s="41"/>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="B76" s="42"/>
-      <c r="C76" s="42"/>
-      <c r="D76" s="42"/>
-      <c r="E76" s="42"/>
-      <c r="F76" s="42"/>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="42"/>
-      <c r="B77" s="42"/>
-      <c r="C77" s="42"/>
-      <c r="D77" s="42"/>
-      <c r="E77" s="42"/>
-      <c r="F77" s="42"/>
+      <c r="A74" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="B74" s="43"/>
+      <c r="D74" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="E74" s="44"/>
+      <c r="F74" s="44"/>
+    </row>
+    <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="B75" s="45"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="B77" s="46"/>
+      <c r="C77" s="46"/>
+      <c r="D77" s="46"/>
+      <c r="E77" s="46"/>
+      <c r="F77" s="46"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="46"/>
+      <c r="B78" s="46"/>
+      <c r="C78" s="46"/>
+      <c r="D78" s="46"/>
+      <c r="E78" s="46"/>
+      <c r="F78" s="46"/>
     </row>
   </sheetData>
-  <mergeCells count="65">
+  <mergeCells count="63">
     <mergeCell ref="D2:F5"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:F12"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="B17:F17"/>
     <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="B30:F30"/>
     <mergeCell ref="E31:F31"/>
     <mergeCell ref="E32:F32"/>
     <mergeCell ref="E33:F33"/>
@@ -1985,7 +2062,7 @@
     <mergeCell ref="E41:F41"/>
     <mergeCell ref="E42:F42"/>
     <mergeCell ref="E43:F43"/>
-    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="B45:F45"/>
     <mergeCell ref="A46:D46"/>
     <mergeCell ref="E46:F46"/>
     <mergeCell ref="A47:D47"/>
@@ -2006,9 +2083,9 @@
     <mergeCell ref="E54:F54"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E55:F55"/>
-    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="B57:F57"/>
     <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="B60:F60"/>
     <mergeCell ref="A61:F61"/>
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="A63:F63"/>
@@ -2018,7 +2095,8 @@
     <mergeCell ref="D67:F67"/>
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="D74:F74"/>
-    <mergeCell ref="A76:F77"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A77:F78"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.511811023622047" footer="0.5"/>

--- a/Hyundai_SND96_CityColor_Quotation.xlsx
+++ b/Hyundai_SND96_CityColor_Quotation.xlsx
@@ -247,7 +247,7 @@
     <t xml:space="preserve">CLIENT ACCEPTANCE — HYUNDAI</t>
   </si>
   <si>
-    <t xml:space="preserve">Adeel Ahmad — Director</t>
+    <t xml:space="preserve">Adeel Ahmed — Director</t>
   </si>
   <si>
     <t xml:space="preserve">Signature, Company Stamp &amp; Date</t>
@@ -914,14 +914,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>76320</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>171360</xdr:rowOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>37800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>2124000</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>56520</xdr:rowOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>190080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -934,8 +934,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="520920" y="15496920"/>
-          <a:ext cx="2047680" cy="723600"/>
+          <a:off x="520920" y="15573240"/>
+          <a:ext cx="2047680" cy="571320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/Hyundai_SND96_CityColor_Quotation.xlsx
+++ b/Hyundai_SND96_CityColor_Quotation.xlsx
@@ -1168,7 +1168,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A2:F78"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
@@ -1176,6 +1176,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="16384" min="7" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Hyundai_SND96_CityColor_Quotation.xlsx
+++ b/Hyundai_SND96_CityColor_Quotation.xlsx
@@ -897,7 +897,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="444600" y="190440"/>
+          <a:off x="533520" y="190440"/>
           <a:ext cx="2857320" cy="780840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -934,7 +934,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="520920" y="15573240"/>
+          <a:off x="609840" y="15573240"/>
           <a:ext cx="2047680" cy="571320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -971,7 +971,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1778040" y="15344640"/>
+          <a:off x="1866960" y="15344640"/>
           <a:ext cx="1266480" cy="980640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1170,12 +1170,11 @@
   <dimension ref="A2:F78"/>
   <sheetFormatPr defaultColWidth="13" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="16384" min="7" style="0" width="13"/>
   </cols>
   <sheetData>

--- a/Hyundai_SND96_CityColor_Quotation.xlsx
+++ b/Hyundai_SND96_CityColor_Quotation.xlsx
@@ -139,7 +139,7 @@
     <t xml:space="preserve">Nos</t>
   </si>
   <si>
-    <t xml:space="preserve">Rental for 15 days @ SAR 160 per unit per day</t>
+    <t xml:space="preserve">Rental for 15 days @ SAR 156 per unit per day</t>
   </si>
   <si>
     <t xml:space="preserve">Transportation to Site</t>
@@ -226,7 +226,7 @@
     <t xml:space="preserve">5.  IMPORTANT NOTES &amp; TERMS</t>
   </si>
   <si>
-    <t xml:space="preserve">•  The rate of SAR 160 per City-Color per day is all-inclusive, covering rental, transportation, installation, accessories, testing, commissioning, technical support, dismantling and removal.</t>
+    <t xml:space="preserve">•  The rate of SAR 156 per City-Color per day is all-inclusive, covering rental, transportation, installation, accessories, testing, commissioning, technical support, dismantling and removal.</t>
   </si>
   <si>
     <t xml:space="preserve">•  Pricing is based on standard installation conditions. Any special access requirements (crane, boom lift, scaffolding, special permits, major electrical works, etc.) will be quoted separately after site assessment.</t>
@@ -1322,11 +1322,11 @@
         <v>15</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F19" s="16" t="n">
         <f aca="false">C19*D19*E19</f>
-        <v>24000</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1343,11 +1343,11 @@
         <v>15</v>
       </c>
       <c r="E20" s="20" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F20" s="21" t="n">
         <f aca="false">C20*D20*E20</f>
-        <v>24000</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1364,11 +1364,11 @@
         <v>15</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F21" s="16" t="n">
         <f aca="false">C21*D21*E21</f>
-        <v>24000</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1385,11 +1385,11 @@
         <v>15</v>
       </c>
       <c r="E22" s="20" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F22" s="21" t="n">
         <f aca="false">C22*D22*E22</f>
-        <v>24000</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1406,11 +1406,11 @@
         <v>15</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">C23*D23*E23</f>
-        <v>24000</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1427,11 +1427,11 @@
         <v>15</v>
       </c>
       <c r="E24" s="20" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F24" s="21" t="n">
         <f aca="false">C24*D24*E24</f>
-        <v>24000</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1448,11 +1448,11 @@
         <v>15</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F25" s="16" t="n">
         <f aca="false">C25*D25*E25</f>
-        <v>24000</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1469,11 +1469,11 @@
         <v>15</v>
       </c>
       <c r="E26" s="20" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F26" s="21" t="n">
         <f aca="false">C26*D26*E26</f>
-        <v>24000</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1490,11 +1490,11 @@
         <v>15</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">C27*D27*E27</f>
-        <v>24000</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="F28" s="24" t="n">
         <f aca="false">SUM(F19:F27)</f>
-        <v>216000</v>
+        <v>210600</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1830,7 +1830,7 @@
       <c r="D50" s="31"/>
       <c r="E50" s="34" t="n">
         <f aca="false">E19</f>
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F50" s="34"/>
     </row>
@@ -1843,7 +1843,7 @@
       <c r="D51" s="31"/>
       <c r="E51" s="34" t="n">
         <f aca="false">E19*15</f>
-        <v>2400</v>
+        <v>2340</v>
       </c>
       <c r="F51" s="34"/>
     </row>
@@ -1856,7 +1856,7 @@
       <c r="D52" s="31"/>
       <c r="E52" s="34" t="n">
         <f aca="false">F19</f>
-        <v>24000</v>
+        <v>23400</v>
       </c>
       <c r="F52" s="34"/>
     </row>
@@ -1869,7 +1869,7 @@
       <c r="D53" s="35"/>
       <c r="E53" s="36" t="n">
         <f aca="false">F28</f>
-        <v>216000</v>
+        <v>210600</v>
       </c>
       <c r="F53" s="36"/>
     </row>
@@ -1882,7 +1882,7 @@
       <c r="D54" s="31"/>
       <c r="E54" s="37" t="n">
         <f aca="false">ROUND(E53*0.15,2)</f>
-        <v>32400</v>
+        <v>31590</v>
       </c>
       <c r="F54" s="37"/>
     </row>
@@ -1895,7 +1895,7 @@
       <c r="D55" s="38"/>
       <c r="E55" s="39" t="n">
         <f aca="false">E53+E54</f>
-        <v>248400</v>
+        <v>242190</v>
       </c>
       <c r="F55" s="39"/>
     </row>
